--- a/collected_excels/tia18/CM08P20 ZH003-ZH003.xlsx
+++ b/collected_excels/tia18/CM08P20 ZH003-ZH003.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devices" sheetId="1" r:id="R948347d918b24edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devices" sheetId="1" r:id="R461bdcad1ef646bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -110,7 +110,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra0e15f90ec4140f7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R605f669fba274d88" cstate="print"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -143,7 +143,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra105c61ae3f1415c" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rea96a4a8180c478b" cstate="print"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -176,7 +176,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra743078fa37f4969" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R556d7505f5a94cd8" cstate="print"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -209,7 +209,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Recba0d5220b14ea1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdc639171ed7945d7" cstate="print"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -305,7 +305,7 @@
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="inlineStr">
         <x:is>
-          <x:t>2026-03-26 21:23:21</x:t>
+          <x:t>2026-03-27 10:42:48</x:t>
         </x:is>
       </x:c>
       <x:c s="2" t="inlineStr">
@@ -362,7 +362,7 @@
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="inlineStr">
         <x:is>
-          <x:t>2026-03-26 21:23:21</x:t>
+          <x:t>2026-03-27 10:42:48</x:t>
         </x:is>
       </x:c>
       <x:c s="2" t="inlineStr">
@@ -419,7 +419,7 @@
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="inlineStr">
         <x:is>
-          <x:t>2026-03-26 21:23:21</x:t>
+          <x:t>2026-03-27 10:42:48</x:t>
         </x:is>
       </x:c>
       <x:c s="2" t="inlineStr">
@@ -476,7 +476,7 @@
     <x:row ht="60" customHeight="1">
       <x:c s="2" t="inlineStr">
         <x:is>
-          <x:t>2026-03-26 21:23:21</x:t>
+          <x:t>2026-03-27 10:42:48</x:t>
         </x:is>
       </x:c>
       <x:c s="2" t="inlineStr">
@@ -533,11 +533,11 @@
   </x:sheetData>
   <x:autoFilter ref="A1:K5"/>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="R7cb12b631db74c95"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="Rf8de704b0d8d47ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R674465702e6c4d50"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rfe646c0b0a234468"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="R8c0f37bc408445f1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="Ra325b6e431f04fcc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R119a3bd1262e4067"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R1b58826fe58e42f0"/>
   </x:hyperlinks>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf49e289de692414a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c84ed9480744f39"/>
 </x:worksheet>
 </file>